--- a/data/teachers_list.xlsx
+++ b/data/teachers_list.xlsx
@@ -2505,7 +2505,7 @@
         <v>11</v>
       </c>
       <c r="E45" s="2">
-        <v>103</v>
+        <v>204</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>12</v>
